--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484198_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484198_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6348</v>
+        <v>4.9456</v>
       </c>
       <c r="E2" t="n">
-        <v>3.314</v>
+        <v>3.5408</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3207</v>
+        <v>1.4049</v>
       </c>
       <c r="G2" t="n">
         <v>4.641</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3905</v>
+        <v>0.7014</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0625</v>
+        <v>0.2892</v>
       </c>
       <c r="U2" t="n">
-        <v>0.328</v>
+        <v>0.4122</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4463</v>
+        <v>2.7931</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3391</v>
+        <v>2.2371</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1072</v>
+        <v>0.556</v>
       </c>
       <c r="G3" t="n">
         <v>3.2976</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5736</v>
+        <v>-0.2267</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1189</v>
+        <v>-0.221</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4546</v>
+        <v>-0.0057</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6745</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9337</v>
+        <v>2.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8625</v>
+        <v>2.0665</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0712</v>
+        <v>0.1834</v>
       </c>
       <c r="G4" t="n">
         <v>2.2925</v>
@@ -766,13 +766,13 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2993</v>
+        <v>0.017</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.238</v>
+        <v>-0.034</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0612</v>
+        <v>0.051</v>
       </c>
       <c r="V4" t="n">
         <v>0.3373</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5837</v>
+        <v>0.7785</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5595</v>
+        <v>0.6609</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1432</v>
+        <v>0.1176</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7862</v>
+        <v>-0.0818</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8795</v>
+        <v>-0.0857</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0039</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4892</v>
+        <v>1.3284</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6925</v>
+        <v>-0.1199</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2034</v>
+        <v>1.4484</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.297</v>
+        <v>-1.4102</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.187</v>
+        <v>0.0342</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.11</v>
+        <v>-1.4444</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9731</v>
+        <v>0.2607</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9216</v>
+        <v>0.1135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0515</v>
+        <v>0.1472</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4012</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2457</v>
+        <v>0.2348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1281</v>
+        <v>-0.6822</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1176</v>
+        <v>0.917</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0818</v>
+        <v>3.28</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0857</v>
+        <v>1.9145</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0039</v>
+        <v>1.3655</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3284</v>
+        <v>3.8133</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1199</v>
+        <v>1.2755</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4484</v>
+        <v>2.5378</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4102</v>
+        <v>-0.5333</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0342</v>
+        <v>0.639</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4444</v>
+        <v>-1.1723</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1822</v>
+        <v>-4.1661</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2721</v>
+        <v>0.2876</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4193</v>
+        <v>-0.1869</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1472</v>
+        <v>0.4746</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7979000000000001</v>
+        <v>-1.349</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4012</v>
+        <v>-0.1425</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0565</v>
+        <v>-0.3423</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.113</v>
+        <v>-2.2551</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1695</v>
+        <v>1.9128</v>
       </c>
       <c r="G7" t="n">
-        <v>3.28</v>
+        <v>0.6057</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9145</v>
+        <v>-2.1669</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3655</v>
+        <v>2.7725</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8133</v>
+        <v>-0.2317</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2755</v>
+        <v>-1.6374</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5378</v>
+        <v>1.4057</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5333</v>
+        <v>0.8374</v>
       </c>
       <c r="N7" t="n">
-        <v>0.639</v>
+        <v>-0.5295</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1723</v>
+        <v>1.3669</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.9838</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-4.1661</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1093</v>
+        <v>0.0439</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6177</v>
+        <v>-0.0396</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7271</v>
+        <v>0.0835</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.349</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1425</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0488</v>
+        <v>-0.7248</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7653</v>
+        <v>-1.7838</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7165</v>
+        <v>1.059</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6057</v>
+        <v>-1.7862</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1669</v>
+        <v>-1.8795</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7725</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2317</v>
+        <v>-1.4892</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6374</v>
+        <v>-1.6925</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4057</v>
+        <v>0.2034</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8374</v>
+        <v>-0.297</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5295</v>
+        <v>-0.187</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3669</v>
+        <v>-0.11</v>
       </c>
       <c r="P8" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6626</v>
+        <v>0.6646</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5498</v>
+        <v>0.6973</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1129</v>
+        <v>-0.0327</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3476</v>
+        <v>-2.6181</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4791</v>
+        <v>-4.2727</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1316</v>
+        <v>1.6546</v>
       </c>
       <c r="G9" t="n">
         <v>-3.098</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>2.278</v>
+        <v>1.0075</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9297</v>
+        <v>0.1361</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3483</v>
+        <v>0.8713</v>
       </c>
       <c r="V9" t="n">
         <v>0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6364</v>
+        <v>-2.7235</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2203</v>
+        <v>-4.2794</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5839</v>
+        <v>1.5558</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0047</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6479</v>
+        <v>0.265</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1109</v>
+        <v>-0.1699</v>
       </c>
       <c r="U10" t="n">
-        <v>0.463</v>
+        <v>0.4349</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8679</v>
+        <v>4.593299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.493499999999999</v>
+        <v>-4.7679</v>
       </c>
       <c r="F11" t="n">
-        <v>9.3614</v>
+        <v>9.3611</v>
       </c>
       <c r="G11" t="n">
         <v>8.146100000000001</v>
@@ -1288,7 +1288,7 @@
         <v>9.698600000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.5474</v>
+        <v>-3.547400000000001</v>
       </c>
       <c r="L11" t="n">
         <v>13.2465</v>
@@ -1312,16 +1312,16 @@
         <v>12.895</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2954</v>
+        <v>3.021</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1407999999999999</v>
+        <v>0.5847</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4364</v>
+        <v>2.4363</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6222999999999999</v>
+        <v>-0.6223</v>
       </c>
       <c r="W11" t="n">
         <v>3.795</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.1289</v>
+        <v>1.9184</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08160000000000001</v>
+        <v>1.3218</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0473</v>
+        <v>0.5967</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7286</v>
+        <v>1.4579</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4436</v>
+        <v>1.7636</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2851</v>
+        <v>-0.3057</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0961</v>
+        <v>2.699</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2929</v>
+        <v>1.4113</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8032</v>
+        <v>1.2877</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3675</v>
+        <v>-1.2412</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1507</v>
+        <v>0.3523</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5182</v>
+        <v>-1.5935</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4642</v>
+        <v>-0.1346</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1758</v>
+        <v>-0.3853</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2884</v>
+        <v>0.2507</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1425</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5743</v>
+        <v>1.6865</v>
       </c>
       <c r="E13" t="n">
         <v>0.9638</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6105</v>
+        <v>0.7227</v>
       </c>
       <c r="G13" t="n">
         <v>0.9525</v>
@@ -1468,13 +1468,13 @@
         <v>0.5952</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3106</v>
+        <v>-0.1984</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0612</v>
+        <v>0.051</v>
       </c>
       <c r="V13" t="n">
         <v>0.3373</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9863</v>
+        <v>1.5585</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.4285</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3799</v>
+        <v>1.987</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.7286</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5177</v>
+        <v>0.4436</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.621</v>
+        <v>0.2851</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8051</v>
+        <v>1.0961</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5605</v>
+        <v>0.2929</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7554</v>
+        <v>0.8032</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9084</v>
+        <v>-0.3675</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.1507</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8655</v>
+        <v>-0.5182</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2284</v>
+        <v>-0.1063</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1304</v>
+        <v>-0.3343</v>
       </c>
       <c r="U14" t="n">
-        <v>0.098</v>
+        <v>0.228</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3373</v>
+        <v>0.1425</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9177</v>
+        <v>1.0484</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7096</v>
+        <v>0.5043</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2081</v>
+        <v>0.544</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4579</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7636</v>
+        <v>3.5177</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3057</v>
+        <v>-2.621</v>
       </c>
       <c r="J15" t="n">
-        <v>2.699</v>
+        <v>1.8051</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4113</v>
+        <v>2.5605</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2877</v>
+        <v>-0.7554</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2412</v>
+        <v>-0.9084</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3523</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5935</v>
+        <v>-1.8655</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1353</v>
+        <v>0.2905</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.0284</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1378</v>
+        <v>0.2621</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5341</v>
+        <v>0.2774</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.4256</v>
+        <v>-0.6156</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9597</v>
+        <v>0.8931</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6375999999999999</v>
+        <v>1.344</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1772</v>
+        <v>-1.26</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8148</v>
+        <v>2.604</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6143</v>
+        <v>2.0426</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-1.6172</v>
       </c>
       <c r="L16" t="n">
-        <v>0.241</v>
+        <v>3.6598</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0233</v>
+        <v>-0.6986</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0325</v>
+        <v>0.3572</v>
       </c>
       <c r="O16" t="n">
         <v>-1.0558</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7774</v>
+        <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7713</v>
+        <v>-0.8006</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6291</v>
+        <v>-0.476</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4004</v>
+        <v>-0.3246</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1947</v>
+        <v>-0.266</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1947</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7896</v>
+        <v>-0.2557</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1258</v>
+        <v>-3.4256</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3362</v>
+        <v>3.17</v>
       </c>
       <c r="G17" t="n">
-        <v>1.344</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.26</v>
+        <v>0.1772</v>
       </c>
       <c r="I17" t="n">
-        <v>2.604</v>
+        <v>-0.8148</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0426</v>
+        <v>-0.6143</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.6172</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6598</v>
+        <v>0.241</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6986</v>
+        <v>-0.0233</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3572</v>
+        <v>1.0325</v>
       </c>
       <c r="O17" t="n">
         <v>-1.0558</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1822</v>
+        <v>2.7774</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8676</v>
+        <v>-0.0185</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9862</v>
+        <v>-0.6291</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8815</v>
+        <v>0.6106</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>-0.1947</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0811</v>
+        <v>-0.6185</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0113</v>
+        <v>1.1133</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0923</v>
+        <v>-1.7319</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5401</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3264</v>
+        <v>0.1361</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2436</v>
+        <v>-0.1416</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0828</v>
+        <v>0.2777</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6189</v>
+        <v>-0.9345</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4947</v>
+        <v>-1.0866</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1242</v>
+        <v>0.1521</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3209</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1591</v>
+        <v>-0.4747</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>-0.34</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.411</v>
+        <v>-0.1347</v>
       </c>
       <c r="V19" t="n">
         <v>0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8927</v>
+        <v>-1.5221</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3757</v>
+        <v>-1.4777</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.517</v>
+        <v>-0.0443</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1739</v>
@@ -2014,13 +2014,13 @@
         <v>3.3725</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9091</v>
+        <v>-0.5384</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2492</v>
+        <v>-0.3513</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6599</v>
+        <v>-0.1872</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9099</v>
+        <v>-1.6616</v>
       </c>
       <c r="E21" t="n">
         <v>-2.9322</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0223</v>
+        <v>1.2706</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7021</v>
@@ -2092,13 +2092,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.271</v>
+        <v>-0.0227</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0056</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2654</v>
+        <v>-0.0171</v>
       </c>
       <c r="V21" t="n">
         <v>-0.532</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7172</v>
+        <v>-4.0044</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3801</v>
+        <v>-3.2984</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.337</v>
+        <v>-0.706</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1513</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2196</v>
+        <v>0.9324</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3661</v>
+        <v>0.4479</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8535</v>
+        <v>0.4845</v>
       </c>
       <c r="V22" t="n">
         <v>1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.868100000000001</v>
+        <v>-2.5076</v>
       </c>
       <c r="E23" t="n">
         <v>-9.3614</v>
       </c>
       <c r="F23" t="n">
-        <v>5.493500000000001</v>
+        <v>6.854000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-8.1462</v>
@@ -2248,13 +2248,13 @@
         <v>18.8466</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.295599999999999</v>
+        <v>-0.9351999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.4364</v>
+        <v>-2.4363</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1407000000000002</v>
+        <v>1.501</v>
       </c>
       <c r="V23" t="n">
         <v>0.6222999999999999</v>
